--- a/campus-placement/qa/C-9-Transactional-Lifecycle-Add-Edit-Delete-View-Cancel.xlsx
+++ b/campus-placement/qa/C-9-Transactional-Lifecycle-Add-Edit-Delete-View-Cancel.xlsx
@@ -615,15 +615,11 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="R2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -703,15 +699,11 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="R3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -791,15 +783,11 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="R4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -879,15 +867,11 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="R5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -967,15 +951,11 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="R6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
